--- a/public/templates/Liste enseignants.xlsx
+++ b/public/templates/Liste enseignants.xlsx
@@ -397,171 +397,283 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I9"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>PPR</v>
+      </c>
+      <c r="B1" t="str">
         <v>Nom</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Prénom</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>Nom (arabe)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Prénom (arabe)</v>
+      </c>
+      <c r="F1" t="str">
         <v>Matière</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
+        <v>Téléphone</v>
+      </c>
+      <c r="H1" t="str">
         <v>Email</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>Mot de passe</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>152340</v>
+      </c>
+      <c r="B2" t="str">
         <v>Bennani</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>Ahmed</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
+        <v>بناني</v>
+      </c>
+      <c r="E2" t="str">
+        <v>أحمد</v>
+      </c>
+      <c r="F2" t="str">
         <v>Mathématiques</v>
       </c>
-      <c r="D2" t="str">
+      <c r="G2" t="str">
+        <v>0662345601</v>
+      </c>
+      <c r="H2" t="str">
         <v>a.bennani@edu.ma</v>
       </c>
-      <c r="E2" t="str">
+      <c r="I2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>152341</v>
+      </c>
+      <c r="B3" t="str">
         <v>Chraibi</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>Fatima Zahra</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
+        <v>الشرابي</v>
+      </c>
+      <c r="E3" t="str">
+        <v>فاطمة الزهراء</v>
+      </c>
+      <c r="F3" t="str">
         <v>Physique-Chimie</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
+        <v>0662345602</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>152342</v>
+      </c>
+      <c r="B4" t="str">
         <v>Daoudi</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>Hassan</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
+        <v>داودي</v>
+      </c>
+      <c r="E4" t="str">
+        <v>حسن</v>
+      </c>
+      <c r="F4" t="str">
         <v>SVT</v>
       </c>
-      <c r="D4" t="str">
+      <c r="G4" t="str">
+        <v>0662345603</v>
+      </c>
+      <c r="H4" t="str">
         <v>h.daoudi@edu.ma</v>
       </c>
-      <c r="E4" t="str">
+      <c r="I4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>152343</v>
+      </c>
+      <c r="B5" t="str">
         <v>Erragragui</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>Khadija</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
+        <v>الرغراغي</v>
+      </c>
+      <c r="E5" t="str">
+        <v>خديجة</v>
+      </c>
+      <c r="F5" t="str">
         <v>Français</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
+      <c r="G5" t="str">
+        <v>0662345604</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>152344</v>
+      </c>
+      <c r="B6" t="str">
         <v>Filali</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>Mostafa</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
+        <v>الفيلالي</v>
+      </c>
+      <c r="E6" t="str">
+        <v>مصطفى</v>
+      </c>
+      <c r="F6" t="str">
         <v>Anglais</v>
       </c>
-      <c r="D6" t="str">
+      <c r="G6" t="str">
+        <v>0662345605</v>
+      </c>
+      <c r="H6" t="str">
         <v>m.filali@edu.ma</v>
       </c>
-      <c r="E6" t="str">
+      <c r="I6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>152345</v>
+      </c>
+      <c r="B7" t="str">
         <v>Guedira</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>Samira</v>
       </c>
-      <c r="C7" t="str">
+      <c r="D7" t="str">
+        <v>كديرة</v>
+      </c>
+      <c r="E7" t="str">
+        <v>سميرة</v>
+      </c>
+      <c r="F7" t="str">
         <v>Arabe</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
+      <c r="G7" t="str">
+        <v>0662345606</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>152346</v>
+      </c>
+      <c r="B8" t="str">
         <v>Hakimi</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>Youssef</v>
       </c>
-      <c r="C8" t="str">
+      <c r="D8" t="str">
+        <v>الحكيمي</v>
+      </c>
+      <c r="E8" t="str">
+        <v>يوسف</v>
+      </c>
+      <c r="F8" t="str">
         <v>EPS</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
+      <c r="G8" t="str">
+        <v>0662345607</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>152347</v>
+      </c>
+      <c r="B9" t="str">
         <v>Idrissi</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>Naima</v>
       </c>
-      <c r="C9" t="str">
+      <c r="D9" t="str">
+        <v>الإدريسي</v>
+      </c>
+      <c r="E9" t="str">
+        <v>نعيمة</v>
+      </c>
+      <c r="F9" t="str">
         <v>Informatique</v>
       </c>
-      <c r="D9" t="str">
+      <c r="G9" t="str">
+        <v>0662345608</v>
+      </c>
+      <c r="H9" t="str">
         <v>n.idrissi@edu.ma</v>
       </c>
-      <c r="E9" t="str">
+      <c r="I9" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>